--- a/output/yearly_population_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_34_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4380</v>
+        <v>4803</v>
       </c>
       <c r="C2" t="n">
-        <v>7570</v>
+        <v>10973</v>
       </c>
       <c r="D2" t="n">
-        <v>21573</v>
+        <v>21357</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2782</v>
+        <v>3469</v>
       </c>
       <c r="C3" t="n">
-        <v>9403</v>
+        <v>7192</v>
       </c>
       <c r="D3" t="n">
-        <v>15345</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>2726</v>
       </c>
       <c r="C4" t="n">
-        <v>7498</v>
+        <v>7819</v>
       </c>
       <c r="D4" t="n">
-        <v>8274</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1535</v>
+        <v>1723</v>
       </c>
       <c r="C5" t="n">
-        <v>6210</v>
+        <v>5601</v>
       </c>
       <c r="D5" t="n">
-        <v>3326</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>858</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>3916</v>
+        <v>3597</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>2401</v>
+        <v>2234</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>1120</v>
+        <v>1088</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
         <v>243</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6436</v>
+        <v>5726</v>
       </c>
       <c r="C2" t="n">
-        <v>6844</v>
+        <v>12170</v>
       </c>
       <c r="D2" t="n">
-        <v>22108</v>
+        <v>17770</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2812</v>
+        <v>3301</v>
       </c>
       <c r="C3" t="n">
-        <v>7630</v>
+        <v>7785</v>
       </c>
       <c r="D3" t="n">
-        <v>15135</v>
+        <v>14668</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2191</v>
+        <v>2592</v>
       </c>
       <c r="C4" t="n">
-        <v>8201</v>
+        <v>7298</v>
       </c>
       <c r="D4" t="n">
-        <v>9108</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>1885</v>
       </c>
       <c r="C5" t="n">
-        <v>6577</v>
+        <v>6463</v>
       </c>
       <c r="D5" t="n">
-        <v>3905</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1025</v>
+        <v>1173</v>
       </c>
       <c r="C6" t="n">
-        <v>4848</v>
+        <v>4375</v>
       </c>
       <c r="D6" t="n">
-        <v>1567</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>609</v>
       </c>
       <c r="C7" t="n">
-        <v>3000</v>
+        <v>2785</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C8" t="n">
-        <v>1623</v>
+        <v>1559</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6230</v>
+        <v>7359</v>
       </c>
       <c r="C2" t="n">
-        <v>8511</v>
+        <v>11019</v>
       </c>
       <c r="D2" t="n">
-        <v>23657</v>
+        <v>17030</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3359</v>
+        <v>3449</v>
       </c>
       <c r="C3" t="n">
-        <v>6547</v>
+        <v>8446</v>
       </c>
       <c r="D3" t="n">
-        <v>14971</v>
+        <v>14101</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2070</v>
+        <v>2447</v>
       </c>
       <c r="C4" t="n">
-        <v>7721</v>
+        <v>7277</v>
       </c>
       <c r="D4" t="n">
-        <v>9553</v>
+        <v>9199</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1677</v>
+        <v>1939</v>
       </c>
       <c r="C5" t="n">
-        <v>7016</v>
+        <v>6665</v>
       </c>
       <c r="D5" t="n">
-        <v>4485</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>1311</v>
       </c>
       <c r="C6" t="n">
-        <v>5471</v>
+        <v>5097</v>
       </c>
       <c r="D6" t="n">
-        <v>1823</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>641</v>
+        <v>735</v>
       </c>
       <c r="C7" t="n">
-        <v>3657</v>
+        <v>3364</v>
       </c>
       <c r="D7" t="n">
-        <v>834</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="C8" t="n">
-        <v>2105</v>
+        <v>2014</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>1017</v>
+        <v>986</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5791</v>
+        <v>6716</v>
       </c>
       <c r="C2" t="n">
-        <v>5991</v>
+        <v>7757</v>
       </c>
       <c r="D2" t="n">
-        <v>19787</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3824</v>
+        <v>4200</v>
       </c>
       <c r="C3" t="n">
-        <v>10511</v>
+        <v>12309</v>
       </c>
       <c r="D3" t="n">
-        <v>16536</v>
+        <v>15686</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1549</v>
+        <v>1791</v>
       </c>
       <c r="C4" t="n">
-        <v>10737</v>
+        <v>10240</v>
       </c>
       <c r="D4" t="n">
-        <v>9287</v>
+        <v>8926</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1069</v>
+        <v>1211</v>
       </c>
       <c r="C5" t="n">
-        <v>5361</v>
+        <v>4995</v>
       </c>
       <c r="D5" t="n">
-        <v>2949</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="C6" t="n">
-        <v>3583</v>
+        <v>3296</v>
       </c>
       <c r="D6" t="n">
-        <v>817</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>2062</v>
+        <v>1973</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>996</v>
+        <v>966</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3494</v>
+        <v>4103</v>
       </c>
       <c r="C2" t="n">
-        <v>2767</v>
+        <v>3962</v>
       </c>
       <c r="D2" t="n">
-        <v>14404</v>
+        <v>10437</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3975</v>
+        <v>4492</v>
       </c>
       <c r="C3" t="n">
-        <v>7797</v>
+        <v>9365</v>
       </c>
       <c r="D3" t="n">
-        <v>16026</v>
+        <v>14630</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>2340</v>
       </c>
       <c r="C4" t="n">
-        <v>10723</v>
+        <v>11353</v>
       </c>
       <c r="D4" t="n">
-        <v>10226</v>
+        <v>9799</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1172</v>
+        <v>1350</v>
       </c>
       <c r="C5" t="n">
-        <v>7622</v>
+        <v>7195</v>
       </c>
       <c r="D5" t="n">
-        <v>3646</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>699</v>
+        <v>798</v>
       </c>
       <c r="C6" t="n">
-        <v>4383</v>
+        <v>4020</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>2595</v>
+        <v>2483</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1306</v>
+        <v>1254</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
         <v>205</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2791</v>
+        <v>3354</v>
       </c>
       <c r="C2" t="n">
-        <v>8592</v>
+        <v>14566</v>
       </c>
       <c r="D2" t="n">
-        <v>12410</v>
+        <v>12528</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3211</v>
+        <v>3642</v>
       </c>
       <c r="C3" t="n">
-        <v>4902</v>
+        <v>6169</v>
       </c>
       <c r="D3" t="n">
-        <v>14882</v>
+        <v>13076</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2425</v>
+        <v>2786</v>
       </c>
       <c r="C4" t="n">
-        <v>9123</v>
+        <v>10181</v>
       </c>
       <c r="D4" t="n">
-        <v>10707</v>
+        <v>10289</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="n">
-        <v>8935</v>
+        <v>8921</v>
       </c>
       <c r="D5" t="n">
-        <v>4545</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>932</v>
       </c>
       <c r="C6" t="n">
-        <v>5710</v>
+        <v>5393</v>
       </c>
       <c r="D6" t="n">
-        <v>1380</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="C7" t="n">
-        <v>3355</v>
+        <v>3138</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1810</v>
+        <v>1723</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D9" t="n">
         <v>261</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>47</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1693</v>
+        <v>2041</v>
       </c>
       <c r="C2" t="n">
-        <v>4149</v>
+        <v>7061</v>
       </c>
       <c r="D2" t="n">
-        <v>8654</v>
+        <v>8771</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3010</v>
+        <v>3455</v>
       </c>
       <c r="C3" t="n">
-        <v>5949</v>
+        <v>8688</v>
       </c>
       <c r="D3" t="n">
-        <v>14291</v>
+        <v>12726</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>3063</v>
       </c>
       <c r="C4" t="n">
-        <v>8599</v>
+        <v>9714</v>
       </c>
       <c r="D4" t="n">
-        <v>11446</v>
+        <v>10793</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1418</v>
+        <v>1623</v>
       </c>
       <c r="C5" t="n">
-        <v>10431</v>
+        <v>10684</v>
       </c>
       <c r="D5" t="n">
-        <v>4643</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>6556</v>
+        <v>6164</v>
       </c>
       <c r="D6" t="n">
-        <v>1332</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>3396</v>
+        <v>3228</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="D8" t="n">
         <v>372</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>162</v>
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2518</v>
+        <v>2922</v>
       </c>
       <c r="C2" t="n">
-        <v>8336</v>
+        <v>9325</v>
       </c>
       <c r="D2" t="n">
-        <v>8000</v>
+        <v>13102</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2143</v>
+        <v>2491</v>
       </c>
       <c r="C3" t="n">
-        <v>4620</v>
+        <v>7131</v>
       </c>
       <c r="D3" t="n">
-        <v>12631</v>
+        <v>11384</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2450</v>
+        <v>2811</v>
       </c>
       <c r="C4" t="n">
-        <v>7224</v>
+        <v>9142</v>
       </c>
       <c r="D4" t="n">
-        <v>11535</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1690</v>
+        <v>1937</v>
       </c>
       <c r="C5" t="n">
-        <v>9522</v>
+        <v>10052</v>
       </c>
       <c r="D5" t="n">
-        <v>5481</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>970</v>
       </c>
       <c r="C6" t="n">
-        <v>8124</v>
+        <v>8053</v>
       </c>
       <c r="D6" t="n">
-        <v>1772</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>4668</v>
+        <v>4351</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2011</v>
+        <v>1938</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
         <v>171</v>
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1791</v>
+        <v>1975</v>
       </c>
       <c r="C2" t="n">
-        <v>5098</v>
+        <v>4964</v>
       </c>
       <c r="D2" t="n">
-        <v>7092</v>
+        <v>9392</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1979</v>
+        <v>2299</v>
       </c>
       <c r="C3" t="n">
-        <v>5462</v>
+        <v>7309</v>
       </c>
       <c r="D3" t="n">
-        <v>11445</v>
+        <v>10975</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2160</v>
+        <v>2510</v>
       </c>
       <c r="C4" t="n">
-        <v>6281</v>
+        <v>8374</v>
       </c>
       <c r="D4" t="n">
-        <v>11431</v>
+        <v>10614</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>2071</v>
       </c>
       <c r="C5" t="n">
-        <v>8826</v>
+        <v>9923</v>
       </c>
       <c r="D5" t="n">
-        <v>6058</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>980</v>
+        <v>1118</v>
       </c>
       <c r="C6" t="n">
-        <v>8872</v>
+        <v>8954</v>
       </c>
       <c r="D6" t="n">
-        <v>2070</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>5765</v>
+        <v>5445</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2592</v>
+        <v>2455</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1975</v>
+        <v>3527</v>
       </c>
       <c r="C2" t="n">
-        <v>7412</v>
+        <v>7863</v>
       </c>
       <c r="D2" t="n">
-        <v>18064</v>
+        <v>17650</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1614</v>
+        <v>1849</v>
       </c>
       <c r="C3" t="n">
-        <v>4754</v>
+        <v>5807</v>
       </c>
       <c r="D3" t="n">
-        <v>10243</v>
+        <v>10112</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1824</v>
+        <v>2121</v>
       </c>
       <c r="C4" t="n">
-        <v>5820</v>
+        <v>7780</v>
       </c>
       <c r="D4" t="n">
-        <v>11085</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1788</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="n">
-        <v>7665</v>
+        <v>9136</v>
       </c>
       <c r="D5" t="n">
-        <v>6486</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1159</v>
+        <v>1319</v>
       </c>
       <c r="C6" t="n">
-        <v>8784</v>
+        <v>9228</v>
       </c>
       <c r="D6" t="n">
-        <v>2541</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>6858</v>
+        <v>6646</v>
       </c>
       <c r="D7" t="n">
-        <v>887</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>3673</v>
+        <v>3420</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1244</v>
+        <v>1186</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3753,7 +3753,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5727</v>
+        <v>5630</v>
       </c>
       <c r="C2" t="n">
-        <v>9633</v>
+        <v>11877</v>
       </c>
       <c r="D2" t="n">
-        <v>20682</v>
+        <v>5532</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1442</v>
+        <v>2602</v>
       </c>
       <c r="C2" t="n">
-        <v>4387</v>
+        <v>4717</v>
       </c>
       <c r="D2" t="n">
-        <v>13439</v>
+        <v>13132</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2138</v>
+        <v>2523</v>
       </c>
       <c r="C3" t="n">
-        <v>5796</v>
+        <v>6906</v>
       </c>
       <c r="D3" t="n">
-        <v>11696</v>
+        <v>11489</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2568</v>
+        <v>2951</v>
       </c>
       <c r="C4" t="n">
-        <v>8471</v>
+        <v>10779</v>
       </c>
       <c r="D4" t="n">
-        <v>11346</v>
+        <v>10692</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1087</v>
+        <v>1218</v>
       </c>
       <c r="C5" t="n">
-        <v>11841</v>
+        <v>13206</v>
       </c>
       <c r="D5" t="n">
-        <v>5939</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="C6" t="n">
-        <v>8270</v>
+        <v>8050</v>
       </c>
       <c r="D6" t="n">
-        <v>1985</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3599</v>
+        <v>3351</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1219</v>
+        <v>1162</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4361,7 +4361,7 @@
         <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>16</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5958</v>
+        <v>7533</v>
       </c>
       <c r="C2" t="n">
-        <v>11561</v>
+        <v>4932</v>
       </c>
       <c r="D2" t="n">
-        <v>19100</v>
+        <v>24852</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2433</v>
+        <v>2392</v>
       </c>
       <c r="C3" t="n">
-        <v>4855</v>
+        <v>5986</v>
       </c>
       <c r="D3" t="n">
-        <v>4113</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4328</v>
+        <v>4730</v>
       </c>
       <c r="C2" t="n">
-        <v>6647</v>
+        <v>9269</v>
       </c>
       <c r="D2" t="n">
-        <v>23813</v>
+        <v>28609</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3446</v>
+        <v>4072</v>
       </c>
       <c r="C3" t="n">
-        <v>7459</v>
+        <v>4647</v>
       </c>
       <c r="D3" t="n">
-        <v>6328</v>
+        <v>5364</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1091</v>
+        <v>1073</v>
       </c>
       <c r="C4" t="n">
-        <v>2889</v>
+        <v>3551</v>
       </c>
       <c r="D4" t="n">
-        <v>2010</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4896,10 +4896,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3915</v>
+        <v>4249</v>
       </c>
       <c r="C2" t="n">
-        <v>6537</v>
+        <v>6841</v>
       </c>
       <c r="D2" t="n">
-        <v>34010</v>
+        <v>28617</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3188</v>
+        <v>3658</v>
       </c>
       <c r="C3" t="n">
-        <v>6091</v>
+        <v>6174</v>
       </c>
       <c r="D3" t="n">
-        <v>8669</v>
+        <v>8696</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1901</v>
+        <v>2149</v>
       </c>
       <c r="C4" t="n">
-        <v>5373</v>
+        <v>4087</v>
       </c>
       <c r="D4" t="n">
-        <v>2777</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C5" t="n">
-        <v>1650</v>
+        <v>2005</v>
       </c>
       <c r="D5" t="n">
-        <v>1309</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5126</v>
+        <v>5846</v>
       </c>
       <c r="C2" t="n">
-        <v>12055</v>
+        <v>8265</v>
       </c>
       <c r="D2" t="n">
-        <v>26898</v>
+        <v>23110</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2907</v>
+        <v>3246</v>
       </c>
       <c r="C3" t="n">
-        <v>5507</v>
+        <v>5677</v>
       </c>
       <c r="D3" t="n">
-        <v>11910</v>
+        <v>11111</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2156</v>
+        <v>2458</v>
       </c>
       <c r="C4" t="n">
-        <v>5640</v>
+        <v>5103</v>
       </c>
       <c r="D4" t="n">
-        <v>3767</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>975</v>
+        <v>1064</v>
       </c>
       <c r="C5" t="n">
-        <v>3509</v>
+        <v>3003</v>
       </c>
       <c r="D5" t="n">
-        <v>1522</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>958</v>
+        <v>1149</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
         <v>474</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6048</v>
+        <v>6360</v>
       </c>
       <c r="C2" t="n">
-        <v>14550</v>
+        <v>14338</v>
       </c>
       <c r="D2" t="n">
-        <v>31803</v>
+        <v>29681</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2871</v>
+        <v>3247</v>
       </c>
       <c r="C3" t="n">
-        <v>7155</v>
+        <v>5717</v>
       </c>
       <c r="D3" t="n">
-        <v>12452</v>
+        <v>11434</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1566</v>
+        <v>1751</v>
       </c>
       <c r="C4" t="n">
-        <v>4507</v>
+        <v>4428</v>
       </c>
       <c r="D4" t="n">
-        <v>4377</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>803</v>
+        <v>914</v>
       </c>
       <c r="C5" t="n">
-        <v>3349</v>
+        <v>2950</v>
       </c>
       <c r="D5" t="n">
-        <v>1509</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>1469</v>
+        <v>1391</v>
       </c>
       <c r="D6" t="n">
-        <v>781</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>412</v>
+        <v>467</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4365</v>
+        <v>5568</v>
       </c>
       <c r="C2" t="n">
-        <v>7827</v>
+        <v>10768</v>
       </c>
       <c r="D2" t="n">
-        <v>24644</v>
+        <v>25009</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3666</v>
+        <v>4001</v>
       </c>
       <c r="C3" t="n">
-        <v>9779</v>
+        <v>9197</v>
       </c>
       <c r="D3" t="n">
-        <v>14786</v>
+        <v>13657</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1927</v>
+        <v>2156</v>
       </c>
       <c r="C4" t="n">
-        <v>5963</v>
+        <v>5103</v>
       </c>
       <c r="D4" t="n">
-        <v>5871</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1039</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="n">
-        <v>3903</v>
+        <v>3739</v>
       </c>
       <c r="D5" t="n">
-        <v>2013</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>2498</v>
+        <v>2242</v>
       </c>
       <c r="D6" t="n">
-        <v>895</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3437</v>
+        <v>4518</v>
       </c>
       <c r="C2" t="n">
-        <v>14243</v>
+        <v>7645</v>
       </c>
       <c r="D2" t="n">
-        <v>23532</v>
+        <v>23946</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3296</v>
+        <v>3944</v>
       </c>
       <c r="C3" t="n">
-        <v>7637</v>
+        <v>8706</v>
       </c>
       <c r="D3" t="n">
-        <v>15243</v>
+        <v>14421</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2371</v>
+        <v>2594</v>
       </c>
       <c r="C4" t="n">
-        <v>7833</v>
+        <v>7237</v>
       </c>
       <c r="D4" t="n">
-        <v>7262</v>
+        <v>6698</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1458</v>
       </c>
       <c r="C5" t="n">
-        <v>4909</v>
+        <v>4345</v>
       </c>
       <c r="D5" t="n">
-        <v>2655</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>686</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>3185</v>
+        <v>2992</v>
       </c>
       <c r="D6" t="n">
-        <v>1075</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1734</v>
+        <v>1619</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D8" t="n">
         <v>402</v>
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6552,7 +6552,7 @@
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_34_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4803</v>
+        <v>5857</v>
       </c>
       <c r="C2" t="n">
-        <v>10973</v>
+        <v>9680</v>
       </c>
       <c r="D2" t="n">
-        <v>21357</v>
+        <v>29653</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3469</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>7192</v>
+        <v>4826</v>
       </c>
       <c r="D3" t="n">
-        <v>14800</v>
+        <v>11609</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2726</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>7819</v>
+        <v>6054</v>
       </c>
       <c r="D4" t="n">
-        <v>7828</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1723</v>
+        <v>1798</v>
       </c>
       <c r="C5" t="n">
-        <v>5601</v>
+        <v>5605</v>
       </c>
       <c r="D5" t="n">
-        <v>3001</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C6" t="n">
-        <v>3597</v>
+        <v>3768</v>
       </c>
       <c r="D6" t="n">
-        <v>1209</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>2046</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1088</v>
+        <v>892</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>434</v>
+        <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5726</v>
+        <v>6698</v>
       </c>
       <c r="C2" t="n">
-        <v>12170</v>
+        <v>8967</v>
       </c>
       <c r="D2" t="n">
-        <v>17770</v>
+        <v>23007</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3301</v>
+        <v>3550</v>
       </c>
       <c r="C3" t="n">
-        <v>7785</v>
+        <v>6157</v>
       </c>
       <c r="D3" t="n">
-        <v>14668</v>
+        <v>13282</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2592</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>7298</v>
+        <v>5292</v>
       </c>
       <c r="D4" t="n">
-        <v>8585</v>
+        <v>7012</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1885</v>
+        <v>1988</v>
       </c>
       <c r="C5" t="n">
-        <v>6463</v>
+        <v>5695</v>
       </c>
       <c r="D5" t="n">
-        <v>3651</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="C6" t="n">
-        <v>4375</v>
+        <v>4506</v>
       </c>
       <c r="D6" t="n">
-        <v>1439</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C7" t="n">
-        <v>2785</v>
+        <v>2804</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C8" t="n">
-        <v>1559</v>
+        <v>1369</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>685</v>
+        <v>583</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7359</v>
+        <v>7587</v>
       </c>
       <c r="C2" t="n">
-        <v>11019</v>
+        <v>13073</v>
       </c>
       <c r="D2" t="n">
-        <v>17030</v>
+        <v>29301</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3449</v>
+        <v>3888</v>
       </c>
       <c r="C3" t="n">
-        <v>8446</v>
+        <v>6479</v>
       </c>
       <c r="D3" t="n">
-        <v>14101</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2447</v>
+        <v>2520</v>
       </c>
       <c r="C4" t="n">
-        <v>7277</v>
+        <v>5555</v>
       </c>
       <c r="D4" t="n">
-        <v>9199</v>
+        <v>7634</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1939</v>
+        <v>1982</v>
       </c>
       <c r="C5" t="n">
-        <v>6665</v>
+        <v>5355</v>
       </c>
       <c r="D5" t="n">
-        <v>4168</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1311</v>
+        <v>1372</v>
       </c>
       <c r="C6" t="n">
-        <v>5097</v>
+        <v>4901</v>
       </c>
       <c r="D6" t="n">
-        <v>1717</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C7" t="n">
-        <v>3364</v>
+        <v>3486</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C8" t="n">
-        <v>2014</v>
+        <v>1903</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>986</v>
+        <v>869</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>431</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6716</v>
+        <v>6938</v>
       </c>
       <c r="C2" t="n">
-        <v>7757</v>
+        <v>8994</v>
       </c>
       <c r="D2" t="n">
-        <v>14300</v>
+        <v>24093</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4200</v>
+        <v>4598</v>
       </c>
       <c r="C3" t="n">
-        <v>12309</v>
+        <v>9977</v>
       </c>
       <c r="D3" t="n">
-        <v>15686</v>
+        <v>14746</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1791</v>
+        <v>1831</v>
       </c>
       <c r="C4" t="n">
-        <v>10240</v>
+        <v>8180</v>
       </c>
       <c r="D4" t="n">
-        <v>8926</v>
+        <v>7397</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1211</v>
+        <v>1267</v>
       </c>
       <c r="C5" t="n">
-        <v>4995</v>
+        <v>4802</v>
       </c>
       <c r="D5" t="n">
-        <v>2763</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C6" t="n">
-        <v>3296</v>
+        <v>3416</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>1864</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>966</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4103</v>
+        <v>4317</v>
       </c>
       <c r="C2" t="n">
-        <v>3962</v>
+        <v>4918</v>
       </c>
       <c r="D2" t="n">
-        <v>10437</v>
+        <v>16792</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4492</v>
+        <v>4805</v>
       </c>
       <c r="C3" t="n">
-        <v>9365</v>
+        <v>8650</v>
       </c>
       <c r="D3" t="n">
-        <v>14630</v>
+        <v>15309</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2340</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="n">
-        <v>11353</v>
+        <v>9152</v>
       </c>
       <c r="D4" t="n">
-        <v>9799</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>1408</v>
       </c>
       <c r="C5" t="n">
-        <v>7195</v>
+        <v>6248</v>
       </c>
       <c r="D5" t="n">
-        <v>3442</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>4020</v>
+        <v>4103</v>
       </c>
       <c r="D6" t="n">
-        <v>971</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -2097,10 +2097,10 @@
         <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>2483</v>
+        <v>2438</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>1254</v>
+        <v>1130</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3354</v>
+        <v>3839</v>
       </c>
       <c r="C2" t="n">
-        <v>14566</v>
+        <v>9627</v>
       </c>
       <c r="D2" t="n">
-        <v>12528</v>
+        <v>12760</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>3865</v>
       </c>
       <c r="C3" t="n">
-        <v>6169</v>
+        <v>6075</v>
       </c>
       <c r="D3" t="n">
-        <v>13076</v>
+        <v>14481</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2786</v>
+        <v>2999</v>
       </c>
       <c r="C4" t="n">
-        <v>10181</v>
+        <v>8803</v>
       </c>
       <c r="D4" t="n">
-        <v>10289</v>
+        <v>9192</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1560</v>
+        <v>1655</v>
       </c>
       <c r="C5" t="n">
-        <v>8921</v>
+        <v>7456</v>
       </c>
       <c r="D5" t="n">
-        <v>4313</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>932</v>
+        <v>969</v>
       </c>
       <c r="C6" t="n">
-        <v>5393</v>
+        <v>5010</v>
       </c>
       <c r="D6" t="n">
-        <v>1314</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C7" t="n">
-        <v>3138</v>
+        <v>3178</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1723</v>
+        <v>1666</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>755</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2041</v>
+        <v>2310</v>
       </c>
       <c r="C2" t="n">
-        <v>7061</v>
+        <v>4602</v>
       </c>
       <c r="D2" t="n">
-        <v>8771</v>
+        <v>8909</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3455</v>
+        <v>3724</v>
       </c>
       <c r="C3" t="n">
-        <v>8688</v>
+        <v>7065</v>
       </c>
       <c r="D3" t="n">
-        <v>12726</v>
+        <v>13977</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3063</v>
+        <v>3304</v>
       </c>
       <c r="C4" t="n">
-        <v>9714</v>
+        <v>8600</v>
       </c>
       <c r="D4" t="n">
-        <v>10793</v>
+        <v>9846</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1623</v>
+        <v>1718</v>
       </c>
       <c r="C5" t="n">
-        <v>10684</v>
+        <v>8869</v>
       </c>
       <c r="D5" t="n">
-        <v>4508</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="C6" t="n">
-        <v>6164</v>
+        <v>6000</v>
       </c>
       <c r="D6" t="n">
-        <v>1272</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>3228</v>
+        <v>3213</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1229</v>
+        <v>1185</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2922</v>
+        <v>3124</v>
       </c>
       <c r="C2" t="n">
-        <v>9325</v>
+        <v>4977</v>
       </c>
       <c r="D2" t="n">
-        <v>13102</v>
+        <v>9135</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2491</v>
+        <v>2674</v>
       </c>
       <c r="C3" t="n">
-        <v>7131</v>
+        <v>5299</v>
       </c>
       <c r="D3" t="n">
-        <v>11384</v>
+        <v>12482</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2811</v>
+        <v>3067</v>
       </c>
       <c r="C4" t="n">
-        <v>9142</v>
+        <v>7781</v>
       </c>
       <c r="D4" t="n">
-        <v>10761</v>
+        <v>10181</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1937</v>
+        <v>2080</v>
       </c>
       <c r="C5" t="n">
-        <v>10052</v>
+        <v>8650</v>
       </c>
       <c r="D5" t="n">
-        <v>5319</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>970</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>8053</v>
+        <v>7189</v>
       </c>
       <c r="D6" t="n">
-        <v>1659</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>4351</v>
+        <v>4367</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1938</v>
+        <v>1923</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1975</v>
+        <v>2131</v>
       </c>
       <c r="C2" t="n">
-        <v>4964</v>
+        <v>3840</v>
       </c>
       <c r="D2" t="n">
-        <v>9392</v>
+        <v>8151</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2299</v>
+        <v>2467</v>
       </c>
       <c r="C3" t="n">
-        <v>7309</v>
+        <v>4753</v>
       </c>
       <c r="D3" t="n">
-        <v>10975</v>
+        <v>11521</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2510</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
-        <v>8374</v>
+        <v>6791</v>
       </c>
       <c r="D4" t="n">
-        <v>10614</v>
+        <v>10256</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2071</v>
+        <v>2266</v>
       </c>
       <c r="C5" t="n">
-        <v>9923</v>
+        <v>8493</v>
       </c>
       <c r="D5" t="n">
-        <v>5834</v>
+        <v>5153</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1118</v>
+        <v>1204</v>
       </c>
       <c r="C6" t="n">
-        <v>8954</v>
+        <v>7928</v>
       </c>
       <c r="D6" t="n">
-        <v>1953</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>5445</v>
+        <v>5328</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2455</v>
+        <v>2479</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
         <v>35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3527</v>
+        <v>3292</v>
       </c>
       <c r="C2" t="n">
-        <v>7863</v>
+        <v>7070</v>
       </c>
       <c r="D2" t="n">
-        <v>17650</v>
+        <v>12280</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1849</v>
+        <v>1979</v>
       </c>
       <c r="C3" t="n">
-        <v>5807</v>
+        <v>3952</v>
       </c>
       <c r="D3" t="n">
-        <v>10112</v>
+        <v>10379</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2121</v>
+        <v>2275</v>
       </c>
       <c r="C4" t="n">
-        <v>7780</v>
+        <v>5808</v>
       </c>
       <c r="D4" t="n">
-        <v>10339</v>
+        <v>10126</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2021</v>
+        <v>2224</v>
       </c>
       <c r="C5" t="n">
-        <v>9136</v>
+        <v>7646</v>
       </c>
       <c r="D5" t="n">
-        <v>6253</v>
+        <v>5682</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1319</v>
+        <v>1429</v>
       </c>
       <c r="C6" t="n">
-        <v>9228</v>
+        <v>8074</v>
       </c>
       <c r="D6" t="n">
-        <v>2356</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="C7" t="n">
-        <v>6646</v>
+        <v>6268</v>
       </c>
       <c r="D7" t="n">
-        <v>861</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>3420</v>
+        <v>3479</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1186</v>
+        <v>1226</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5630</v>
+        <v>4415</v>
       </c>
       <c r="C2" t="n">
-        <v>11877</v>
+        <v>5890</v>
       </c>
       <c r="D2" t="n">
-        <v>5532</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2602</v>
+        <v>2380</v>
       </c>
       <c r="C2" t="n">
-        <v>4717</v>
+        <v>4073</v>
       </c>
       <c r="D2" t="n">
-        <v>13132</v>
+        <v>9136</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2523</v>
+        <v>2686</v>
       </c>
       <c r="C3" t="n">
-        <v>6906</v>
+        <v>4998</v>
       </c>
       <c r="D3" t="n">
-        <v>11489</v>
+        <v>11331</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2951</v>
+        <v>3215</v>
       </c>
       <c r="C4" t="n">
-        <v>10779</v>
+        <v>8377</v>
       </c>
       <c r="D4" t="n">
-        <v>10692</v>
+        <v>10404</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1218</v>
+        <v>1361</v>
       </c>
       <c r="C5" t="n">
-        <v>13206</v>
+        <v>11327</v>
       </c>
       <c r="D5" t="n">
-        <v>5619</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>406</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>8050</v>
+        <v>7646</v>
       </c>
       <c r="D6" t="n">
-        <v>1873</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3351</v>
+        <v>3409</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1162</v>
+        <v>1201</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7533</v>
+        <v>6357</v>
       </c>
       <c r="C2" t="n">
-        <v>4932</v>
+        <v>8449</v>
       </c>
       <c r="D2" t="n">
-        <v>24852</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2392</v>
+        <v>1877</v>
       </c>
       <c r="C3" t="n">
-        <v>5986</v>
+        <v>3015</v>
       </c>
       <c r="D3" t="n">
-        <v>1568</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4730</v>
+        <v>4817</v>
       </c>
       <c r="C2" t="n">
-        <v>9269</v>
+        <v>7167</v>
       </c>
       <c r="D2" t="n">
-        <v>28609</v>
+        <v>21071</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4072</v>
+        <v>3377</v>
       </c>
       <c r="C3" t="n">
-        <v>4647</v>
+        <v>5319</v>
       </c>
       <c r="D3" t="n">
-        <v>5364</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1073</v>
+        <v>849</v>
       </c>
       <c r="C4" t="n">
-        <v>3551</v>
+        <v>1809</v>
       </c>
       <c r="D4" t="n">
-        <v>1497</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4249</v>
+        <v>5467</v>
       </c>
       <c r="C2" t="n">
-        <v>6841</v>
+        <v>8903</v>
       </c>
       <c r="D2" t="n">
-        <v>28617</v>
+        <v>18723</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>3355</v>
       </c>
       <c r="C3" t="n">
-        <v>6174</v>
+        <v>5476</v>
       </c>
       <c r="D3" t="n">
-        <v>8696</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2149</v>
+        <v>1785</v>
       </c>
       <c r="C4" t="n">
-        <v>4087</v>
+        <v>3759</v>
       </c>
       <c r="D4" t="n">
-        <v>2193</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>492</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>2005</v>
+        <v>1084</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5846</v>
+        <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>8265</v>
+        <v>10706</v>
       </c>
       <c r="D2" t="n">
-        <v>23110</v>
+        <v>25428</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3246</v>
+        <v>3570</v>
       </c>
       <c r="C3" t="n">
-        <v>5677</v>
+        <v>6301</v>
       </c>
       <c r="D3" t="n">
-        <v>11111</v>
+        <v>7878</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2458</v>
+        <v>2179</v>
       </c>
       <c r="C4" t="n">
-        <v>5103</v>
+        <v>4567</v>
       </c>
       <c r="D4" t="n">
-        <v>3312</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1064</v>
+        <v>896</v>
       </c>
       <c r="C5" t="n">
-        <v>3003</v>
+        <v>2473</v>
       </c>
       <c r="D5" t="n">
-        <v>1326</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>1149</v>
+        <v>696</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6360</v>
+        <v>6489</v>
       </c>
       <c r="C2" t="n">
-        <v>14338</v>
+        <v>10143</v>
       </c>
       <c r="D2" t="n">
-        <v>29681</v>
+        <v>23652</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3247</v>
+        <v>3296</v>
       </c>
       <c r="C3" t="n">
-        <v>5717</v>
+        <v>7005</v>
       </c>
       <c r="D3" t="n">
-        <v>11434</v>
+        <v>9399</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1751</v>
+        <v>1771</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>4524</v>
       </c>
       <c r="D4" t="n">
-        <v>4045</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>914</v>
+        <v>802</v>
       </c>
       <c r="C5" t="n">
-        <v>2950</v>
+        <v>2583</v>
       </c>
       <c r="D5" t="n">
-        <v>1319</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="C6" t="n">
-        <v>1391</v>
+        <v>1071</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>467</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5568</v>
+        <v>5620</v>
       </c>
       <c r="C2" t="n">
-        <v>10768</v>
+        <v>5675</v>
       </c>
       <c r="D2" t="n">
-        <v>25009</v>
+        <v>21210</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4001</v>
+        <v>4071</v>
       </c>
       <c r="C3" t="n">
-        <v>9197</v>
+        <v>7600</v>
       </c>
       <c r="D3" t="n">
-        <v>13657</v>
+        <v>11101</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2156</v>
+        <v>2227</v>
       </c>
       <c r="C4" t="n">
-        <v>5103</v>
+        <v>5930</v>
       </c>
       <c r="D4" t="n">
-        <v>5411</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>3739</v>
+        <v>3665</v>
       </c>
       <c r="D5" t="n">
-        <v>1789</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>2242</v>
+        <v>1903</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>973</v>
+        <v>751</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4518</v>
+        <v>3834</v>
       </c>
       <c r="C2" t="n">
-        <v>7645</v>
+        <v>5303</v>
       </c>
       <c r="D2" t="n">
-        <v>23946</v>
+        <v>15465</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3944</v>
+        <v>3971</v>
       </c>
       <c r="C3" t="n">
-        <v>8706</v>
+        <v>5742</v>
       </c>
       <c r="D3" t="n">
-        <v>14421</v>
+        <v>11919</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2594</v>
+        <v>2705</v>
       </c>
       <c r="C4" t="n">
-        <v>7237</v>
+        <v>6679</v>
       </c>
       <c r="D4" t="n">
-        <v>6698</v>
+        <v>5447</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="C5" t="n">
-        <v>4345</v>
+        <v>4828</v>
       </c>
       <c r="D5" t="n">
-        <v>2395</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>2992</v>
+        <v>2811</v>
       </c>
       <c r="D6" t="n">
-        <v>994</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>1619</v>
+        <v>1341</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>654</v>
+        <v>520</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_34_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5857</v>
+        <v>1622</v>
       </c>
       <c r="C2" t="n">
-        <v>9680</v>
+        <v>2670</v>
       </c>
       <c r="D2" t="n">
-        <v>29653</v>
+        <v>14747</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>2360</v>
       </c>
       <c r="C3" t="n">
-        <v>4826</v>
+        <v>6771</v>
       </c>
       <c r="D3" t="n">
-        <v>11609</v>
+        <v>14672</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>1251</v>
       </c>
       <c r="C4" t="n">
-        <v>6054</v>
+        <v>6971</v>
       </c>
       <c r="D4" t="n">
-        <v>6347</v>
+        <v>7392</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1798</v>
+        <v>673</v>
       </c>
       <c r="C5" t="n">
-        <v>5605</v>
+        <v>2984</v>
       </c>
       <c r="D5" t="n">
-        <v>2521</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>972</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>3768</v>
+        <v>988</v>
       </c>
       <c r="D6" t="n">
-        <v>1099</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>2046</v>
+        <v>466</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>892</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>37</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6698</v>
+        <v>1692</v>
       </c>
       <c r="C2" t="n">
-        <v>8967</v>
+        <v>6464</v>
       </c>
       <c r="D2" t="n">
-        <v>23007</v>
+        <v>18810</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3550</v>
+        <v>1681</v>
       </c>
       <c r="C3" t="n">
-        <v>6157</v>
+        <v>3925</v>
       </c>
       <c r="D3" t="n">
-        <v>13282</v>
+        <v>13627</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>1551</v>
       </c>
       <c r="C4" t="n">
-        <v>5292</v>
+        <v>6779</v>
       </c>
       <c r="D4" t="n">
-        <v>7012</v>
+        <v>8565</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>846</v>
       </c>
       <c r="C5" t="n">
-        <v>5695</v>
+        <v>5093</v>
       </c>
       <c r="D5" t="n">
-        <v>3007</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1197</v>
+        <v>421</v>
       </c>
       <c r="C6" t="n">
-        <v>4506</v>
+        <v>2002</v>
       </c>
       <c r="D6" t="n">
-        <v>1302</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>2804</v>
+        <v>726</v>
       </c>
       <c r="D7" t="n">
-        <v>700</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1369</v>
+        <v>397</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>583</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7587</v>
+        <v>871</v>
       </c>
       <c r="C2" t="n">
-        <v>13073</v>
+        <v>2600</v>
       </c>
       <c r="D2" t="n">
-        <v>29301</v>
+        <v>12737</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3888</v>
+        <v>1618</v>
       </c>
       <c r="C3" t="n">
-        <v>6479</v>
+        <v>4733</v>
       </c>
       <c r="D3" t="n">
-        <v>13598</v>
+        <v>13919</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2520</v>
+        <v>1731</v>
       </c>
       <c r="C4" t="n">
-        <v>5555</v>
+        <v>6175</v>
       </c>
       <c r="D4" t="n">
-        <v>7634</v>
+        <v>9298</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1982</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>5355</v>
+        <v>6206</v>
       </c>
       <c r="D5" t="n">
-        <v>3492</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1372</v>
+        <v>346</v>
       </c>
       <c r="C6" t="n">
-        <v>4901</v>
+        <v>2782</v>
       </c>
       <c r="D6" t="n">
-        <v>1501</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>742</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>3486</v>
+        <v>767</v>
       </c>
       <c r="D7" t="n">
-        <v>775</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>335</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1903</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>869</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6938</v>
+        <v>743</v>
       </c>
       <c r="C2" t="n">
-        <v>8994</v>
+        <v>6162</v>
       </c>
       <c r="D2" t="n">
-        <v>24093</v>
+        <v>11759</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4598</v>
+        <v>1085</v>
       </c>
       <c r="C3" t="n">
-        <v>9977</v>
+        <v>3160</v>
       </c>
       <c r="D3" t="n">
-        <v>14746</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1831</v>
+        <v>1475</v>
       </c>
       <c r="C4" t="n">
-        <v>8180</v>
+        <v>5316</v>
       </c>
       <c r="D4" t="n">
-        <v>7397</v>
+        <v>9858</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1267</v>
+        <v>1123</v>
       </c>
       <c r="C5" t="n">
-        <v>4802</v>
+        <v>6180</v>
       </c>
       <c r="D5" t="n">
-        <v>2409</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>685</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>3416</v>
+        <v>4423</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>1864</v>
+        <v>1709</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>600</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
+        <v>329</v>
+      </c>
+      <c r="D9" t="n">
         <v>375</v>
-      </c>
-      <c r="D9" t="n">
-        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4317</v>
+        <v>473</v>
       </c>
       <c r="C2" t="n">
-        <v>4918</v>
+        <v>3834</v>
       </c>
       <c r="D2" t="n">
-        <v>16792</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4805</v>
+        <v>832</v>
       </c>
       <c r="C3" t="n">
-        <v>8650</v>
+        <v>4129</v>
       </c>
       <c r="D3" t="n">
-        <v>15309</v>
+        <v>11982</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>1234</v>
       </c>
       <c r="C4" t="n">
-        <v>9152</v>
+        <v>4323</v>
       </c>
       <c r="D4" t="n">
-        <v>8301</v>
+        <v>10098</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1408</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="n">
-        <v>6248</v>
+        <v>5915</v>
       </c>
       <c r="D5" t="n">
-        <v>3004</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>646</v>
       </c>
       <c r="C6" t="n">
-        <v>4103</v>
+        <v>5261</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2438</v>
+        <v>2693</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>891</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3839</v>
+        <v>1186</v>
       </c>
       <c r="C2" t="n">
-        <v>9627</v>
+        <v>6693</v>
       </c>
       <c r="D2" t="n">
-        <v>12760</v>
+        <v>15733</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3865</v>
+        <v>573</v>
       </c>
       <c r="C3" t="n">
-        <v>6075</v>
+        <v>3528</v>
       </c>
       <c r="D3" t="n">
-        <v>14481</v>
+        <v>10664</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2999</v>
+        <v>928</v>
       </c>
       <c r="C4" t="n">
-        <v>8803</v>
+        <v>4136</v>
       </c>
       <c r="D4" t="n">
-        <v>9192</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1655</v>
+        <v>1121</v>
       </c>
       <c r="C5" t="n">
-        <v>7456</v>
+        <v>5084</v>
       </c>
       <c r="D5" t="n">
-        <v>3726</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>969</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>5010</v>
+        <v>5504</v>
       </c>
       <c r="D6" t="n">
-        <v>1216</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>3178</v>
+        <v>3850</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>1666</v>
+        <v>1641</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2310</v>
+        <v>787</v>
       </c>
       <c r="C2" t="n">
-        <v>4602</v>
+        <v>3426</v>
       </c>
       <c r="D2" t="n">
-        <v>8909</v>
+        <v>11327</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3724</v>
+        <v>894</v>
       </c>
       <c r="C3" t="n">
-        <v>7065</v>
+        <v>4704</v>
       </c>
       <c r="D3" t="n">
-        <v>13977</v>
+        <v>11782</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3304</v>
+        <v>1488</v>
       </c>
       <c r="C4" t="n">
-        <v>8600</v>
+        <v>5800</v>
       </c>
       <c r="D4" t="n">
-        <v>9846</v>
+        <v>10658</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1718</v>
+        <v>837</v>
       </c>
       <c r="C5" t="n">
-        <v>8869</v>
+        <v>7598</v>
       </c>
       <c r="D5" t="n">
-        <v>3937</v>
+        <v>5443</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>6000</v>
+        <v>5229</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3213</v>
+        <v>1608</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>590</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3124</v>
+        <v>420</v>
       </c>
       <c r="C2" t="n">
-        <v>4977</v>
+        <v>3047</v>
       </c>
       <c r="D2" t="n">
-        <v>9135</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2674</v>
+        <v>712</v>
       </c>
       <c r="C3" t="n">
-        <v>5299</v>
+        <v>3574</v>
       </c>
       <c r="D3" t="n">
-        <v>12482</v>
+        <v>10871</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3067</v>
+        <v>1008</v>
       </c>
       <c r="C4" t="n">
-        <v>7781</v>
+        <v>4965</v>
       </c>
       <c r="D4" t="n">
-        <v>10181</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2080</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>8650</v>
+        <v>5920</v>
       </c>
       <c r="D5" t="n">
-        <v>4668</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1028</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>7189</v>
+        <v>5201</v>
       </c>
       <c r="D6" t="n">
-        <v>1551</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>4367</v>
+        <v>2280</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1923</v>
+        <v>660</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>574</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2131</v>
+        <v>556</v>
       </c>
       <c r="C2" t="n">
-        <v>3840</v>
+        <v>9227</v>
       </c>
       <c r="D2" t="n">
-        <v>8151</v>
+        <v>17443</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2467</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>4753</v>
+        <v>2869</v>
       </c>
       <c r="D3" t="n">
-        <v>11521</v>
+        <v>9651</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>761</v>
       </c>
       <c r="C4" t="n">
-        <v>6791</v>
+        <v>4073</v>
       </c>
       <c r="D4" t="n">
-        <v>10256</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2266</v>
+        <v>814</v>
       </c>
       <c r="C5" t="n">
-        <v>8493</v>
+        <v>5331</v>
       </c>
       <c r="D5" t="n">
-        <v>5153</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1204</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>7928</v>
+        <v>5515</v>
       </c>
       <c r="D6" t="n">
-        <v>1847</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>5328</v>
+        <v>3789</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>862</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>2479</v>
+        <v>1444</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>443</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3292</v>
+        <v>649</v>
       </c>
       <c r="C2" t="n">
-        <v>7070</v>
+        <v>10434</v>
       </c>
       <c r="D2" t="n">
-        <v>12280</v>
+        <v>20905</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1979</v>
+        <v>422</v>
       </c>
       <c r="C3" t="n">
-        <v>3952</v>
+        <v>5326</v>
       </c>
       <c r="D3" t="n">
-        <v>10379</v>
+        <v>10109</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2275</v>
+        <v>551</v>
       </c>
       <c r="C4" t="n">
-        <v>5808</v>
+        <v>3325</v>
       </c>
       <c r="D4" t="n">
-        <v>10126</v>
+        <v>9492</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2224</v>
+        <v>715</v>
       </c>
       <c r="C5" t="n">
-        <v>7646</v>
+        <v>4580</v>
       </c>
       <c r="D5" t="n">
-        <v>5682</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1429</v>
+        <v>582</v>
       </c>
       <c r="C6" t="n">
-        <v>8074</v>
+        <v>5366</v>
       </c>
       <c r="D6" t="n">
-        <v>2235</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>490</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>6268</v>
+        <v>4616</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>3479</v>
+        <v>2523</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1226</v>
+        <v>884</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4415</v>
+        <v>4127</v>
       </c>
       <c r="C2" t="n">
-        <v>5890</v>
+        <v>3909</v>
       </c>
       <c r="D2" t="n">
-        <v>6107</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2380</v>
+        <v>735</v>
       </c>
       <c r="C2" t="n">
-        <v>4073</v>
+        <v>7713</v>
       </c>
       <c r="D2" t="n">
-        <v>9136</v>
+        <v>21431</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2686</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>4998</v>
+        <v>6697</v>
       </c>
       <c r="D3" t="n">
-        <v>11331</v>
+        <v>10897</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3215</v>
+        <v>429</v>
       </c>
       <c r="C4" t="n">
-        <v>8377</v>
+        <v>4165</v>
       </c>
       <c r="D4" t="n">
-        <v>10404</v>
+        <v>9304</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1361</v>
+        <v>597</v>
       </c>
       <c r="C5" t="n">
-        <v>11327</v>
+        <v>3906</v>
       </c>
       <c r="D5" t="n">
-        <v>5186</v>
+        <v>6822</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>452</v>
+        <v>589</v>
       </c>
       <c r="C6" t="n">
-        <v>7646</v>
+        <v>4967</v>
       </c>
       <c r="D6" t="n">
-        <v>1812</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>3409</v>
+        <v>4892</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>1201</v>
+        <v>3403</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>1542</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>518</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6357</v>
+        <v>4797</v>
       </c>
       <c r="C2" t="n">
-        <v>8449</v>
+        <v>4502</v>
       </c>
       <c r="D2" t="n">
-        <v>16300</v>
+        <v>29891</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1877</v>
+        <v>1364</v>
       </c>
       <c r="C3" t="n">
-        <v>3015</v>
+        <v>1543</v>
       </c>
       <c r="D3" t="n">
-        <v>1714</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4817</v>
+        <v>2712</v>
       </c>
       <c r="C2" t="n">
-        <v>7167</v>
+        <v>3079</v>
       </c>
       <c r="D2" t="n">
-        <v>21071</v>
+        <v>23672</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3377</v>
+        <v>2606</v>
       </c>
       <c r="C3" t="n">
-        <v>5319</v>
+        <v>2859</v>
       </c>
       <c r="D3" t="n">
-        <v>4038</v>
+        <v>7355</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>849</v>
+        <v>656</v>
       </c>
       <c r="C4" t="n">
-        <v>1809</v>
+        <v>1010</v>
       </c>
       <c r="D4" t="n">
-        <v>1526</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5467</v>
+        <v>1628</v>
       </c>
       <c r="C2" t="n">
-        <v>8903</v>
+        <v>3568</v>
       </c>
       <c r="D2" t="n">
-        <v>18723</v>
+        <v>25986</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3355</v>
+        <v>2193</v>
       </c>
       <c r="C3" t="n">
-        <v>5476</v>
+        <v>2567</v>
       </c>
       <c r="D3" t="n">
-        <v>6472</v>
+        <v>9554</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1785</v>
+        <v>1434</v>
       </c>
       <c r="C4" t="n">
-        <v>3759</v>
+        <v>2107</v>
       </c>
       <c r="D4" t="n">
-        <v>1961</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>326</v>
       </c>
       <c r="C5" t="n">
-        <v>1084</v>
+        <v>672</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>1583</v>
       </c>
       <c r="C2" t="n">
-        <v>10706</v>
+        <v>9799</v>
       </c>
       <c r="D2" t="n">
-        <v>25428</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3570</v>
+        <v>1585</v>
       </c>
       <c r="C3" t="n">
-        <v>6301</v>
+        <v>2698</v>
       </c>
       <c r="D3" t="n">
-        <v>7878</v>
+        <v>11495</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2179</v>
+        <v>1569</v>
       </c>
       <c r="C4" t="n">
-        <v>4567</v>
+        <v>2328</v>
       </c>
       <c r="D4" t="n">
-        <v>2724</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>896</v>
+        <v>746</v>
       </c>
       <c r="C5" t="n">
-        <v>2473</v>
+        <v>1457</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="C6" t="n">
-        <v>696</v>
+        <v>478</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6489</v>
+        <v>2355</v>
       </c>
       <c r="C2" t="n">
-        <v>10143</v>
+        <v>7315</v>
       </c>
       <c r="D2" t="n">
-        <v>23652</v>
+        <v>22759</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3296</v>
+        <v>1310</v>
       </c>
       <c r="C3" t="n">
-        <v>7005</v>
+        <v>5634</v>
       </c>
       <c r="D3" t="n">
-        <v>9399</v>
+        <v>12094</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1771</v>
+        <v>1370</v>
       </c>
       <c r="C4" t="n">
-        <v>4524</v>
+        <v>2485</v>
       </c>
       <c r="D4" t="n">
-        <v>3124</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>802</v>
+        <v>994</v>
       </c>
       <c r="C5" t="n">
-        <v>2583</v>
+        <v>1894</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>413</v>
       </c>
       <c r="C6" t="n">
-        <v>1071</v>
+        <v>980</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>331</v>
+        <v>387</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5620</v>
+        <v>4165</v>
       </c>
       <c r="C2" t="n">
-        <v>5675</v>
+        <v>10603</v>
       </c>
       <c r="D2" t="n">
-        <v>21210</v>
+        <v>26924</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4071</v>
+        <v>1469</v>
       </c>
       <c r="C3" t="n">
-        <v>7600</v>
+        <v>5652</v>
       </c>
       <c r="D3" t="n">
-        <v>11101</v>
+        <v>12863</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2227</v>
+        <v>1167</v>
       </c>
       <c r="C4" t="n">
-        <v>5930</v>
+        <v>4095</v>
       </c>
       <c r="D4" t="n">
-        <v>4264</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1046</v>
       </c>
       <c r="C5" t="n">
-        <v>3665</v>
+        <v>2155</v>
       </c>
       <c r="D5" t="n">
-        <v>1550</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491</v>
+        <v>610</v>
       </c>
       <c r="C6" t="n">
-        <v>1903</v>
+        <v>1417</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>751</v>
+        <v>667</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3834</v>
+        <v>3544</v>
       </c>
       <c r="C2" t="n">
-        <v>5303</v>
+        <v>6361</v>
       </c>
       <c r="D2" t="n">
-        <v>15465</v>
+        <v>21016</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3971</v>
+        <v>2033</v>
       </c>
       <c r="C3" t="n">
-        <v>5742</v>
+        <v>8843</v>
       </c>
       <c r="D3" t="n">
-        <v>11919</v>
+        <v>14581</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>966</v>
       </c>
       <c r="C4" t="n">
-        <v>6679</v>
+        <v>4702</v>
       </c>
       <c r="D4" t="n">
-        <v>5447</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>563</v>
       </c>
       <c r="C5" t="n">
-        <v>4828</v>
+        <v>1388</v>
       </c>
       <c r="D5" t="n">
-        <v>1983</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>214</v>
       </c>
       <c r="C6" t="n">
-        <v>2811</v>
+        <v>653</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1341</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>520</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
